--- a/sheets/대금율보/검수/바람같은 사람.xlsx
+++ b/sheets/대금율보/검수/바람같은 사람.xlsx
@@ -4825,8 +4825,7 @@
       <c r="G10" s="26"/>
       <c r="H10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="I10" s="26"/>
@@ -4854,8 +4853,7 @@
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-‹</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="G11" s="24" t="inlineStr">
@@ -5378,8 +5376,7 @@
       <c r="J23" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">浹浹
-–淋
-‹</t>
+–淋</t>
         </is>
       </c>
       <c r="K23" s="24"/>

--- a/sheets/대금율보/검수/바람같은 사람.xlsx
+++ b/sheets/대금율보/검수/바람같은 사람.xlsx
@@ -4463,22 +4463,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="121.21" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="90.45" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="K3" s="24"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="90.45" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="K4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="90.45" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="K5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="90.45" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="K6" s="26"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="90.45" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="K7" s="24"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="90.45" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="K8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="90.45" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="K9" s="28"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="90.45" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="23"/>
       <c r="C10" s="26"/>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="K10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="90.45" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="23"/>
       <c r="C11" s="24"/>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="K11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="90.45" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="23"/>
       <c r="C12" s="25"/>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="K12" s="25"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="90.45" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="23"/>
       <c r="C13" s="25"/>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="K13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="90.45" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="23"/>
       <c r="C14" s="26"/>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="K14" s="26"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="90.45" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="23"/>
       <c r="C15" s="24"/>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="K15" s="24"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="90.45" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="23"/>
       <c r="C16" s="25"/>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="K16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="90.45" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="23"/>
       <c r="C17" s="25"/>
@@ -5125,7 +5125,7 @@
       </c>
       <c r="K17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="90.45" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="23"/>
       <c r="C18" s="26"/>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="K18" s="26"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="90.45" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="23"/>
       <c r="C19" s="24"/>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="K19" s="24"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="90.45" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="23"/>
       <c r="C20" s="25"/>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="K20" s="25"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="90.45" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="23"/>
       <c r="C21" s="25"/>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="K21" s="25"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="90.45" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="23"/>
       <c r="C22" s="26"/>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="K22" s="26"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="90.45" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="23"/>
       <c r="C23" s="24"/>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="K23" s="24"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="90.45" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="23"/>
       <c r="C24" s="25"/>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="K24" s="25"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="90.45" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="23"/>
       <c r="C25" s="25"/>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="K25" s="25"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="90.45" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="23"/>
       <c r="C26" s="26"/>
@@ -5486,6 +5486,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="52"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="33"/>
 </worksheet>
 </file>